--- a/docs/synthesis/key-words.xlsx
+++ b/docs/synthesis/key-words.xlsx
@@ -9,14 +9,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,19 +40,6 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
       <scheme val="minor"/>
@@ -90,7 +77,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -150,64 +137,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -224,24 +158,14 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -590,7 +514,7 @@
   <cols>
     <col width="43.42578125" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="59.7109375" customWidth="1" min="3" max="3"/>
+    <col width="73.28515625" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -616,7 +540,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="90" customHeight="1">
+    <row r="2" ht="39" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>geography</t>
@@ -632,15 +556,14 @@
           <t>Africa OR "sub-Saharan Africa" OR "East Africa" OR "West Africa" OR "Central Africa" OR "Southern Africa" OR "North Africa" OR Kenya OR Ethiopia OR Uganda OR Tanzania OR Rwanda OR Burundi OR Ghana OR Nigeria OR Senegal OR Mali OR "Burkina Faso" OR Niger OR Zambia OR Malawi OR Zimbabwe OR Mozambique OR Madagascar OR "South Africa" OR Cameroon OR Congo OR Sudan OR Somalia OR Morocco OR Tunisia OR Egypt</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n"/>
-    </row>
-    <row r="3" ht="39" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+    </row>
+    <row r="3" ht="51.75" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>outcome1</t>
         </is>
       </c>
-      <c r="B3" s="21" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
@@ -650,33 +573,31 @@
           <t>adoption OR "adoption rate" OR "adoption probability" OR "technology adoption" OR "farmer adoption" OR uptake OR "willingness to adopt" OR "participation rate" OR diffusion OR scaling</t>
         </is>
       </c>
-      <c r="D3" s="21" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+    </row>
+    <row r="4" ht="64.5" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>outcome2</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>cost OR costs OR "production cost" OR "total cost" OR "implementation cost" OR "establishment cost" OR "installation cost" OR "initial cost" OR "upfront cost" OR "capital cost" OR CAPEX OR "investment cost" OR "operating cost" OR OPEX OR "maintenance cost" OR "recurrent cost" OR "management cost" OR "input cost" OR "variable cost" OR "labour cost" OR "labor cost" OR "labour requirement" OR "labor requirement" OR "opportunity cost" OR "land opportunity cost" OR "foregone income" OR "transaction cost" OR "monitoring cost" OR "verification cost" OR "MRV cost" OR "certification cost" OR "abatement cost" OR "marginal abatement cost" OR "economic analysis" OR "economic evaluation" OR "financial analysis" OR "cost-benefit analysis" OR "cost benefit analysis" OR profitability OR profit OR "net income" OR "net return" OR "gross margin" OR "return on investment" OR ROI OR "net present value" OR NPV OR "internal rate of return" OR IRR OR "payback period" OR "benefit-cost ratio" OR "benefit cost ratio" OR BCR OR "cost-effectiveness" OR "cost effectiveness"</t>
-        </is>
-      </c>
-      <c r="D4" s="23" t="n"/>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>(cost OR costs OR "production cost" OR "total cost" OR "implementation cost" OR "establishment cost" OR "installation cost" OR "initial cost" OR "upfront cost" OR "capital cost" OR CAPEX OR "investment cost" OR "operating cost" OR OPEX OR "maintenance cost" OR "recurrent cost" OR "management cost" OR "input cost" OR "variable cost" OR "labour cost" OR "labor cost" OR "labour requirement" OR "labor requirement" OR "opportunity cost" OR "land opportunity cost" OR "foregone income" OR "transaction cost" OR "monitoring cost" OR "verification cost" OR "MRV cost" OR "certification cost" OR "abatement cost" OR "marginal abatement cost" OR "economic analysis" OR "economic evaluation" OR "financial analysis" OR "cost-benefit analysis" OR "cost benefit analysis" OR profitability OR profit OR "net income" OR "net return" OR "gross margin" OR "return on investment" OR ROI OR "net present value" OR NPV OR "internal rate of return" OR IRR OR "payback period" OR "benefit-cost ratio" OR "benefit cost ratio" OR BCR OR "cost-effectiveness" OR "cost effectiveness" OR incentive* OR subsid* OR payment* OR compensation OR reward* OR grant* OR voucher* OR rebate* OR "cash transfer*" OR "financial support" OR "cost sharing" OR "price premium*" OR "payment* for ecosystem services" OR "payment* for environmental services" OR "carbon payment*" OR "carbon credit*" OR "causal effect*" OR "causal impact*" OR "impact evaluation" OR "treatment effect*" OR experiment* OR randomi* OR RCT OR "quasi-experiment*" OR "difference-in-differences" OR "difference in differences" OR "instrumental variable*" OR "regression discontinuity" OR "propensity score*" OR "natural experiment*")</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64.5" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>outcome3</t>
         </is>
       </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Outcome</t>
         </is>
@@ -686,316 +607,263 @@
           <t>"carbon credit" OR "carbon market" OR "payment for ecosystem services" OR PES OR "REDD+" OR "voluntary carbon market" OR "carbon income" OR "carbon revenue" OR "carbon payment" OR "benefit sharing" OR "revenue sharing" OR "smallholder income" OR "farmer income" OR "income share" OR "carbon benefit"</t>
         </is>
       </c>
-      <c r="D5" s="21" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+    </row>
+    <row r="6" ht="26.25" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>water_management</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Water management</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>"alternate wetting and drying" OR AWD OR "moderate AWD" OR "intermittent irrigation" OR "irrigated rice" OR "rice irrigation" OR "water-saving irrigation" OR "controlled irrigation"</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n"/>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+    </row>
+    <row r="7" ht="39" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>rice_establishment</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Rice establishment</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>"direct seeded rice" OR "direct-seeded rice" OR DSR OR "dry direct seeding" OR "wet direct seeding" OR "System of Rice Intensification" OR SRI OR "rice establishment" OR "intermittent irrigation" OR "younger seedlings" OR "wide spacing"</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+    </row>
+    <row r="8" ht="51.75" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>soil_fertility</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Soil fertility &amp; nutrient-use efficiency</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>"integrated soil fertility management" OR ISFM OR "nutrient use efficiency" OR "fertilizer use efficiency" OR "nutrient management" OR "fertilizer placement" OR "fertilizer timing" OR "microdosing" OR "mineral fertilizer" OR manure OR "green manure" OR "organic inputs" OR "integrated nutrient management"</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+    </row>
+    <row r="9" ht="39" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>soil_cover</t>
         </is>
       </c>
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Soil cover / moisture &amp; erosion</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>"soil cover" OR mulch OR mulching OR "organic mulch" OR "crop residue mulch" OR "surface mulch" OR "straw mulch" OR "cover crop" OR "cover crops" OR "living mulch" OR "vegetative cover" OR "surface residue" OR "residue cover" OR "residue retention" OR "crop residue retention" OR "residue management"</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+    </row>
+    <row r="10" ht="26.25" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>reduced_tillage</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Reduced tillage</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>"reduced tillage" OR "minimum tillage" OR "zero tillage" OR "no till" OR "no-till" OR "conservation tillage" OR "conservation agriculture"</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    </row>
+    <row r="11" ht="39" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>soil_condition</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Soil condition &amp; water retention</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>biochar OR "bio-char" OR "biochar amendment" OR "biochar application" OR "pyrochar" OR "soil water holding capacity" OR "plant available water" OR "acidic soil" OR "degraded soil"</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+    </row>
+    <row r="12" ht="39" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>tree_microclimate</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Tree-based microclimate &amp; soil-water buffering</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>agroforestry OR "trees on farms" OR "trees in farmlands" OR "on-farm trees" OR parkland OR "parkland agroforestry" OR "alley cropping" OR "alley intercropping" OR "tree-crop intercropping" OR "scattered trees" OR "Faidherbia albida" OR "tree density" OR "canopy cover"</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+    </row>
+    <row r="13" ht="64.5" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>tree_wind</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Tree-based wind/shelter buffering</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>windbreak OR windbreaks OR shelterbelt OR shelterbelts OR hedgerow OR hedgerows OR "living fence" OR "boundary planting" OR "wind erosion"</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>? NOT MOVING FORWARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+    </row>
+    <row r="14" ht="51.75" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>tree_soil_fertility</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Tree-based soil fertility</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>"improved fallow" OR "leguminous fallow" OR "tree fallow" OR Sesbania OR Tephrosia OR Gliricidia OR "short rotation fallow"</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>? NOT MOVING FORWARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+    </row>
+    <row r="15" ht="39" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>riparian</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Riparian / erosion buffering</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>"riparian buffer" OR "riparian buffers" OR "riparian vegetation" OR "buffer strip" OR "streambank protection" OR "riverbank protection" OR "bank erosion" OR "water quality" OR "overbank flow"</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>? NOT MOVING FORWARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    </row>
+    <row r="16" ht="51.75" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>livestock_feed</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Livestock feed-buffering</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>"fodder bank" OR "fodder banks" OR "forage bank" OR "feed bank" OR "standing fodder" OR "stored fodder" OR "dry season fodder" OR "dry season feed" OR "feed reserve" OR "fodder reserve"</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+    </row>
+    <row r="17" ht="64.5" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>livestock_emissions</t>
         </is>
       </c>
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Livestock feed security &amp; emissions intensity</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>"feed management" OR "improved feeding" OR "feed quality" OR "forage quality" OR "planted forage" OR "legume forage" OR "crop residue feeding" OR "crop residue management" OR hay OR silage OR "conserved feed" OR "dry season supplementation" OR "strategic supplementation" OR "mixed crop-livestock" OR dairy</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+    </row>
+    <row r="18" ht="64.5" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>rangeland</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Rangeland / forage resilience</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>"rotational grazing" OR "planned grazing" OR "grazing management" OR "managed grazing" OR "sustainable rangeland management" OR "grazing rotation" OR "rested pasture" OR "grazing exclusion" OR "standing hay reserve" OR "forage productivity" OR "grazing pressure"</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    </row>
+    <row r="19" ht="39" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>tree_livestock</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>Tree-livestock heat &amp; feed buffering</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>silvopastoral OR silvopastoralism OR "trees and livestock" OR "shade for livestock" OR "heat stress livestock" OR "fodder trees" OR "browse species" OR "tree-livestock system"</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    </row>
+    <row r="20" ht="51.75" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>soil_amendment</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>Soil amendment / crop condition</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>"enhanced rock weathering" OR ERW OR "enhanced weathering" OR "basalt application" OR "basalt amendment" OR "basalt dust" OR "rock dust" OR "silicate rock amendment" OR "rock powder" OR "soil pH amelioration"</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>EVIDENCE LIMITED- JORDAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="64.5" customHeight="1"/>
-    <row r="23" ht="39" customHeight="1"/>
-    <row r="24" ht="51.75" customHeight="1"/>
-    <row r="25" ht="64.5" customHeight="1"/>
-    <row r="26" ht="64.5" customHeight="1"/>
-    <row r="27" ht="26.25" customHeight="1"/>
-    <row r="28" ht="39" customHeight="1"/>
-    <row r="29" ht="51.75" customHeight="1"/>
-    <row r="30" ht="39" customHeight="1"/>
-    <row r="31" ht="26.25" customHeight="1"/>
-    <row r="32" ht="39" customHeight="1"/>
-    <row r="33" ht="39" customHeight="1"/>
-    <row r="34" ht="64.5" customHeight="1"/>
-    <row r="35" ht="51.75" customHeight="1"/>
-    <row r="36" ht="39" customHeight="1"/>
-    <row r="37" ht="51.75" customHeight="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A4:A21"/>
-    <mergeCell ref="B4:B21"/>
-    <mergeCell ref="D4:D21"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
